--- a/Team-Data/2013-14/5-14-2013-14.xlsx
+++ b/Team-Data/2013-14/5-14-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>5-14-2013-14</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
